--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,41 +1027,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644774</v>
+        <v>129644778</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>96364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R5" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,38 +1138,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644778</v>
+        <v>129644774</v>
       </c>
       <c r="B6" t="n">
-        <v>96352</v>
+        <v>92907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580398</v>
+        <v>580643</v>
       </c>
       <c r="R6" t="n">
-        <v>6510797</v>
+        <v>6510940</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92889</v>
+        <v>92895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129644778</v>
       </c>
       <c r="B5" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>129644774</v>
       </c>
       <c r="B6" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92895</v>
+        <v>92896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -1027,38 +1027,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644778</v>
+        <v>129644774</v>
       </c>
       <c r="B5" t="n">
-        <v>96365</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580398</v>
+        <v>580643</v>
       </c>
       <c r="R5" t="n">
-        <v>6510797</v>
+        <v>6510940</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,41 +1141,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644774</v>
+        <v>129644778</v>
       </c>
       <c r="B6" t="n">
-        <v>92908</v>
+        <v>96365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R6" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129644774</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>129644778</v>
       </c>
       <c r="B6" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92896</v>
+        <v>92901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -1027,41 +1027,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644774</v>
+        <v>129644778</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>96370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R5" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,38 +1138,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644778</v>
+        <v>129644774</v>
       </c>
       <c r="B6" t="n">
-        <v>96370</v>
+        <v>92913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580398</v>
+        <v>580643</v>
       </c>
       <c r="R6" t="n">
-        <v>6510797</v>
+        <v>6510940</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129644778</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>129644774</v>
       </c>
       <c r="B6" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92901</v>
+        <v>92905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,38 +1027,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644778</v>
+        <v>129644774</v>
       </c>
       <c r="B5" t="n">
-        <v>96374</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580398</v>
+        <v>580643</v>
       </c>
       <c r="R5" t="n">
-        <v>6510797</v>
+        <v>6510940</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,41 +1141,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644774</v>
+        <v>129644778</v>
       </c>
       <c r="B6" t="n">
-        <v>92917</v>
+        <v>96376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R6" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92905</v>
+        <v>92907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -1144,7 +1144,7 @@
         <v>129644778</v>
       </c>
       <c r="B6" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129644774</v>
       </c>
       <c r="B5" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>129644778</v>
       </c>
       <c r="B6" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92907</v>
+        <v>92910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,41 +1027,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644774</v>
+        <v>129644778</v>
       </c>
       <c r="B5" t="n">
-        <v>92922</v>
+        <v>96393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R5" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,38 +1138,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644778</v>
+        <v>129644774</v>
       </c>
       <c r="B6" t="n">
-        <v>96390</v>
+        <v>92925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580398</v>
+        <v>580643</v>
       </c>
       <c r="R6" t="n">
-        <v>6510797</v>
+        <v>6510940</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92910</v>
+        <v>92913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129644771</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,38 +1027,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644778</v>
+        <v>129644774</v>
       </c>
       <c r="B5" t="n">
-        <v>96393</v>
+        <v>92926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580398</v>
+        <v>580643</v>
       </c>
       <c r="R5" t="n">
-        <v>6510797</v>
+        <v>6510940</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,41 +1141,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644774</v>
+        <v>129644778</v>
       </c>
       <c r="B6" t="n">
-        <v>92925</v>
+        <v>96394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R6" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1255,7 @@
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92913</v>
+        <v>92914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64644874</v>
+        <v>129644778</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ostlänken Nyköpings kommun, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580713.104182721</v>
+        <v>580398</v>
       </c>
       <c r="R2" t="n">
-        <v>6510980.025485147</v>
+        <v>6510797</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>CallunaAB</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,53 +774,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tenna Toftegaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64644884</v>
+        <v>64645060</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580544.9477664127</v>
+        <v>580440</v>
       </c>
       <c r="R3" t="n">
-        <v>6510809.823564254</v>
+        <v>6511050</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-10-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129644771</v>
+        <v>64644873</v>
       </c>
       <c r="B4" t="n">
-        <v>92888</v>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,40 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Ostlänken Nyköpings kommun, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580398</v>
+        <v>580790</v>
       </c>
       <c r="R4" t="n">
-        <v>6510797</v>
+        <v>6511010</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,22 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2015-10-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,22 +982,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Tenna Toftegaard</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Birgitta Hamstedt</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644774</v>
+        <v>129644771</v>
       </c>
       <c r="B5" t="n">
-        <v>92926</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,28 +1009,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1069,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580643</v>
+        <v>580398</v>
       </c>
       <c r="R5" t="n">
-        <v>6510940</v>
+        <v>6510797</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,52 +1108,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129644778</v>
+        <v>122744275</v>
       </c>
       <c r="B6" t="n">
-        <v>96394</v>
+        <v>91995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Svart- Ö, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580398</v>
+        <v>580474</v>
       </c>
       <c r="R6" t="n">
-        <v>6510797</v>
+        <v>6510768</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,22 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1193,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Birgitta Hamstedt</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>129644773</v>
       </c>
       <c r="B7" t="n">
-        <v>92914</v>
+        <v>93223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,6 +1320,553 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>64644874</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ostlänken Nyköpings kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580713</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6510980</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tenna Toftegaard</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129644774</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>580643</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6510940</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129644770</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580503</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6510928</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>64644884</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ostlänken Nyköpings kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>580545</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6510810</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tenna Toftegaard</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129644779</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>580444</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6510951</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52020-2025 artfynd.xlsx
+++ b/artfynd/A 52020-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644778</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64645060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64644873</t>
         </is>
       </c>
     </row>
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644771</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744275</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644773</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
           <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64644874</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644774</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644770</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64644884</t>
         </is>
       </c>
     </row>
@@ -1867,8 +1922,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>